--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:27:22+00:00</t>
+    <t>2026-09-23T10:03:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:03:14+00:00</t>
+    <t>2026-09-23T14:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T14:46:48+00:00</t>
+    <t>2026-09-24T09:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T09:27:45+00:00</t>
+    <t>2026-09-25T09:45:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T09:45:00+00:00</t>
+    <t>2026-09-26T09:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-26T09:29:37+00:00</t>
+    <t>2026-09-27T10:09:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-27T10:09:28+00:00</t>
+    <t>2026-09-28T11:09:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:09:48+00:00</t>
+    <t>2026-09-29T10:52:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:52:00+00:00</t>
+    <t>2026-09-29T13:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T13:43:38+00:00</t>
+    <t>2026-09-30T10:41:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:41:03+00:00</t>
+    <t>2026-10-01T11:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:07:40+00:00</t>
+    <t>2026-10-02T10:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T10:41:24+00:00</t>
+    <t>2026-10-03T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-03T10:00:18+00:00</t>
+    <t>2026-10-04T10:43:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-04T10:43:31+00:00</t>
+    <t>2026-10-05T07:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T07:30:04+00:00</t>
+    <t>2026-10-05T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T07:43:03+00:00</t>
+    <t>2026-10-05T11:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T11:46:22+00:00</t>
+    <t>2026-10-05T12:26:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T12:26:48+00:00</t>
+    <t>2026-10-06T11:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T11:27:13+00:00</t>
+    <t>2026-10-07T11:16:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:16:58+00:00</t>
+    <t>2026-10-08T11:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T11:33:45+00:00</t>
+    <t>2026-10-09T06:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:26:39+00:00</t>
+    <t>2026-10-09T06:55:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:55:29+00:00</t>
+    <t>2026-10-09T11:29:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T11:29:21+00:00</t>
+    <t>2026-10-10T10:45:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-10T10:45:57+00:00</t>
+    <t>2026-10-11T10:58:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T10:58:45+00:00</t>
+    <t>2026-10-12T12:20:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:20:16+00:00</t>
+    <t>2026-10-13T12:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:04:04+00:00</t>
+    <t>2026-10-14T09:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T09:40:27+00:00</t>
+    <t>2026-10-15T09:19:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:19:06+00:00</t>
+    <t>2026-10-16T09:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:12:55+00:00</t>
+    <t>2026-10-17T08:45:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T08:45:02+00:00</t>
+    <t>2026-10-18T09:00:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:00:27+00:00</t>
+    <t>2026-10-19T10:09:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T10:09:54+00:00</t>
+    <t>2026-10-20T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T09:35:26+00:00</t>
+    <t>2026-10-21T09:32:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:32:52+00:00</t>
+    <t>2026-10-22T09:34:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:34:18+00:00</t>
+    <t>2026-10-23T09:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:12+00:00</t>
+    <t>2026-10-24T09:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-24T09:01:58+00:00</t>
+    <t>2026-10-25T09:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-25T09:18:44+00:00</t>
+    <t>2026-10-26T10:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T10:24:31+00:00</t>
+    <t>2026-10-27T09:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T09:59:02+00:00</t>
+    <t>2026-10-28T10:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:46:00+00:00</t>
+    <t>2026-10-29T11:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:02:34+00:00</t>
+    <t>2026-10-30T10:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mii-cm-kds-vs-canonicals-2026-2027.xlsx
+++ b/mii-cm-kds-vs-canonicals-2026-2027.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T10:59:23+00:00</t>
+    <t>2026-10-31T10:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
